--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.10500896627034</v>
+        <v>3.59206395701893</v>
       </c>
       <c r="D2" t="n">
-        <v>12.69730418305351</v>
+        <v>2.063311929746196</v>
       </c>
       <c r="E2" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F2" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.1346271516672</v>
+        <v>2.78437691214592</v>
       </c>
       <c r="D3" t="n">
-        <v>13.98395611331585</v>
+        <v>2.272392868413825</v>
       </c>
       <c r="E3" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F3" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.10275408036508</v>
+        <v>8.954197538059326</v>
       </c>
       <c r="D4" t="n">
-        <v>43.51255848187048</v>
+        <v>7.070790753303953</v>
       </c>
       <c r="E4" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F4" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.20273563506402</v>
+        <v>6.857944540697904</v>
       </c>
       <c r="D5" t="n">
-        <v>34.84970353600285</v>
+        <v>5.663076824600463</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F5" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.7564327094508</v>
+        <v>7.597920315285755</v>
       </c>
       <c r="D6" t="n">
-        <v>45.76232207996784</v>
+        <v>7.436377337994775</v>
       </c>
       <c r="E6" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F6" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.98714168297541</v>
+        <v>6.985410523483504</v>
       </c>
       <c r="D7" t="n">
-        <v>41.85867546518964</v>
+        <v>6.802034763093317</v>
       </c>
       <c r="E7" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F7" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.08568493092157</v>
+        <v>4.563923801274755</v>
       </c>
       <c r="D8" t="n">
-        <v>26.96483566782377</v>
+        <v>4.381785796021362</v>
       </c>
       <c r="E8" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F8" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.42906516990988</v>
+        <v>6.732223090110355</v>
       </c>
       <c r="D9" t="n">
-        <v>41.44888721788424</v>
+        <v>6.735444172906189</v>
       </c>
       <c r="E9" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F9" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.368848791083169</v>
+        <v>1.197437928551015</v>
       </c>
       <c r="D10" t="n">
-        <v>6.281165341562067</v>
+        <v>1.020689368003836</v>
       </c>
       <c r="E10" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F10" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.53173826990167</v>
+        <v>5.936407468859021</v>
       </c>
       <c r="D11" t="n">
-        <v>33.58408291140314</v>
+        <v>5.45741347310301</v>
       </c>
       <c r="E11" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F11" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.32672987229106</v>
+        <v>3.465593604247297</v>
       </c>
       <c r="D12" t="n">
-        <v>21.54114963235613</v>
+        <v>3.500436815257872</v>
       </c>
       <c r="E12" t="n">
-        <v>13.92563635601586</v>
+        <v>2.262915907852578</v>
       </c>
       <c r="F12" t="n">
-        <v>13.25697189689934</v>
+        <v>2.154257933246142</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
